--- a/ASND.xlsx
+++ b/ASND.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEDE7F42-8FBE-4935-B507-94F6D0C16D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8AEC2B-3040-4D6C-99DB-89192DA4F680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50100" yWindow="2280" windowWidth="22875" windowHeight="18315" xr2:uid="{2734C5C3-33DF-4A68-91F9-B8E8FFD9BE4F}"/>
+    <workbookView xWindow="350" yWindow="1040" windowWidth="19050" windowHeight="19840" xr2:uid="{2734C5C3-33DF-4A68-91F9-B8E8FFD9BE4F}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="73">
   <si>
     <t>Price</t>
   </si>
@@ -68,9 +68,6 @@
     <t>MC</t>
   </si>
   <si>
-    <t>Cash</t>
-  </si>
-  <si>
     <t>Debt</t>
   </si>
   <si>
@@ -273,6 +270,12 @@
   </si>
   <si>
     <t>MOA</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Cash EUR</t>
   </si>
 </sst>
 </file>
@@ -282,7 +285,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -301,12 +304,6 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -902,56 +899,56 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4DE2054-6D94-40E2-B91A-78070665C073}">
   <dimension ref="B2:L13"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" customWidth="1"/>
-    <col min="6" max="7" width="16.28515625" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.7265625" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" customWidth="1"/>
+    <col min="3" max="3" width="19.54296875" customWidth="1"/>
+    <col min="4" max="4" width="11.26953125" customWidth="1"/>
+    <col min="5" max="5" width="19.1796875" customWidth="1"/>
+    <col min="6" max="7" width="16.26953125" customWidth="1"/>
+    <col min="9" max="9" width="6.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="17" t="s">
         <v>17</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="J2" t="s">
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>126.75</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="14">
         <v>44433</v>
@@ -962,24 +959,24 @@
         <v>1</v>
       </c>
       <c r="K3" s="7">
-        <v>58.231000000000002</v>
+        <v>62.376846</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="14"/>
       <c r="G4" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H4" s="18"/>
       <c r="J4" t="s">
@@ -987,31 +984,31 @@
       </c>
       <c r="K4" s="7">
         <f>+K2*K3</f>
-        <v>7380.7792500000005</v>
+        <v>15157.573578</v>
       </c>
       <c r="L4" s="5"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G5" s="13"/>
       <c r="H5" s="17"/>
       <c r="J5" t="s">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="K5" s="7">
-        <v>259</v>
+        <v>573</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="3"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
@@ -1020,22 +1017,22 @@
       <c r="G6" s="15"/>
       <c r="H6" s="19"/>
       <c r="J6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" s="7">
-        <f>219.052+432.19+21.397</f>
-        <v>672.63900000000001</v>
+        <f>448.176+386.106+62.382</f>
+        <v>896.66399999999987</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>11</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>12</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -1043,19 +1040,19 @@
       <c r="G7" s="15"/>
       <c r="H7" s="19"/>
       <c r="J7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K7" s="7">
         <f>+K4-K5+K6</f>
-        <v>7794.4182500000006</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+        <v>15481.237578</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
@@ -1063,12 +1060,12 @@
       <c r="G8" s="15"/>
       <c r="H8" s="19"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>14</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>15</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
@@ -1076,22 +1073,22 @@
       <c r="G9" s="15"/>
       <c r="H9" s="19"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>48</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>49</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
       <c r="F10" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G10" s="15"/>
       <c r="H10" s="19"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
@@ -1100,7 +1097,7 @@
       <c r="G11" s="15"/>
       <c r="H11" s="19"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
@@ -1109,7 +1106,7 @@
       <c r="G12" s="15"/>
       <c r="H12" s="19"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
@@ -1126,70 +1123,70 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0BFE991-EB13-4971-84D4-47487AF983B8}">
   <dimension ref="A1:CJ28"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="17" width="9.140625" style="5"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="17" width="9.1796875" style="5"/>
     <col min="34" max="34" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>30</v>
-      </c>
       <c r="K2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="O2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="P2" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="T2">
         <v>2019</v>
@@ -1239,9 +1236,9 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -1271,9 +1268,9 @@
         <v>360</v>
       </c>
     </row>
-    <row r="4" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -1294,9 +1291,9 @@
         <v>240</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -1317,9 +1314,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -1340,9 +1337,9 @@
         <v>250</v>
       </c>
     </row>
-    <row r="7" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -1363,9 +1360,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -1386,9 +1383,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -1409,9 +1406,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -1432,7 +1429,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -1449,9 +1446,9 @@
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
     </row>
-    <row r="12" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -1514,9 +1511,9 @@
         <v>161.0510000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -1599,9 +1596,9 @@
         <v>760.73347350000006</v>
       </c>
     </row>
-    <row r="14" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" s="11" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -1685,9 +1682,9 @@
         <v>921.7844735000001</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
@@ -1745,9 +1742,9 @@
         <v>92.178447350000013</v>
       </c>
     </row>
-    <row r="16" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -1810,9 +1807,9 @@
         <v>829.60602615000005</v>
       </c>
     </row>
-    <row r="17" spans="2:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -1834,9 +1831,9 @@
       <c r="P17" s="10"/>
       <c r="Q17" s="10"/>
     </row>
-    <row r="18" spans="2:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -1889,9 +1886,9 @@
         <v>214.42707042140199</v>
       </c>
     </row>
-    <row r="19" spans="2:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -1947,9 +1944,9 @@
         <v>214.42707042140199</v>
       </c>
     </row>
-    <row r="20" spans="2:88" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:88" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -2005,9 +2002,9 @@
         <v>615.17895572859811</v>
       </c>
     </row>
-    <row r="21" spans="2:88" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:88" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X21" s="9">
         <v>0</v>
@@ -2034,9 +2031,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:88" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:88" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="X22" s="9">
         <f>+X20+X21</f>
@@ -2071,9 +2068,9 @@
         <v>615.17895572859811</v>
       </c>
     </row>
-    <row r="23" spans="2:88" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:88" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="X23" s="9">
         <v>0</v>
@@ -2107,9 +2104,9 @@
         <v>30.758947786429907</v>
       </c>
     </row>
-    <row r="24" spans="2:88" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:88" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X24" s="9">
         <f>+X22-X23</f>
@@ -2372,7 +2369,7 @@
         <v>329.55747588281412</v>
       </c>
     </row>
-    <row r="25" spans="2:88" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:88" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>1</v>
       </c>
@@ -2412,9 +2409,9 @@
         <v>10.436071570395862</v>
       </c>
     </row>
-    <row r="26" spans="2:88" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:88" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="X26" s="9">
         <v>56</v>
@@ -2448,27 +2445,27 @@
         <v>56</v>
       </c>
       <c r="AG26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AH26" s="21">
         <v>0.09</v>
       </c>
     </row>
-    <row r="27" spans="2:88" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:88" x14ac:dyDescent="0.25">
       <c r="AG27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AH27" s="21">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="28" spans="2:88" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:88" x14ac:dyDescent="0.25">
       <c r="AG28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AH28" s="7">
         <f>NPV(AH26,Y24:CJ24)+Main!K5-Main!K6</f>
-        <v>4425.5470028423515</v>
+        <v>4515.5220028423519</v>
       </c>
     </row>
   </sheetData>
@@ -2485,23 +2482,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DFC1ADA-BB4A-4FAA-A26D-E4D074BEE288}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="6.26953125" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
         <v>37</v>
-      </c>
-      <c r="C2" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
